--- a/ewatch_data/meter_export_reading.xlsx
+++ b/ewatch_data/meter_export_reading.xlsx
@@ -25,7 +25,7 @@
     <t>Parameter: Abs Active Energy (kWh)</t>
   </si>
   <si>
-    <t xml:space="preserve">Duration(dd/mm/yyyy): 04/06/2026 </t>
+    <t xml:space="preserve">Duration(dd/mm/yyyy): 08/06/2026 </t>
   </si>
   <si>
     <t>INSTITUTIONAL Area</t>
@@ -406,13 +406,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B3">
-        <v>16474262</v>
+        <v>16508048</v>
       </c>
       <c r="C3">
-        <v>5472786</v>
+        <v>5508771</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -421,7 +421,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LNote : Blank column/s = data unavailable 
- Printed Date : 05/06/2026 06:25:33 PM 
+ Printed Date : 09/06/2026 01:37:03 PM 
  Daily meter reading will be the first reading of the day where meter is successfully connected.</oddFooter>
   </headerFooter>
 </worksheet>
